--- a/artfynd/A 35620-2023 artfynd.xlsx
+++ b/artfynd/A 35620-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35620-2023 artfynd.xlsx
+++ b/artfynd/A 35620-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111845306</v>
+        <v>112991797</v>
       </c>
       <c r="B12" t="n">
-        <v>96720</v>
+        <v>99554</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2004,57 +2004,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brinken, SV (mellrsta) (knärot), Vstm</t>
+          <t>Brinken NV, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564522</v>
+        <v>564654</v>
       </c>
       <c r="R12" t="n">
-        <v>6615783</v>
+        <v>6616460</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2076,24 +2068,14 @@
           <t>Sura</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>U-Sur-0535</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>X: (7) 30 pl, A: 186/320 (5), 7 pl, 1 bl, B. 183/292 (4), 100 pl, 4 bl, C:205/297 (0)50 pl (5 m från tänkt basväg)</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,29 +2088,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blandskog kring skogsbäck</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111845440</v>
+        <v>112992615</v>
       </c>
       <c r="B13" t="n">
-        <v>96720</v>
+        <v>89993</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2137,57 +2120,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brinken, SV, (mellersta, syd) (knärot), Vstm</t>
+          <t>Brinken NV, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564551</v>
+        <v>564633</v>
       </c>
       <c r="R13" t="n">
-        <v>6615754</v>
+        <v>6616352</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2209,24 +2179,14 @@
           <t>Sura</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>U-Sur-0536</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>X. (7), 150 pl, A: 192/262 (4), 20 pl, 3 bl, (5 m från tänkt basväg B: 2307243 (4), 60 pl, 10 bl.</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2239,33 +2199,39 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Blandskog kring skogsbäck</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112991797</v>
+        <v>112990960</v>
       </c>
       <c r="B14" t="n">
-        <v>99554</v>
+        <v>56717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2274,31 +2240,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2339,25 +2309,29 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Blandskog kring skogsbäck</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2371,246 +2345,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112992615</v>
-      </c>
-      <c r="B15" t="n">
-        <v>89993</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Brinken NV, Vstm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>564633</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6616352</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Blandskog kring skogsbäck</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112990960</v>
-      </c>
-      <c r="B16" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>102621</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Sparvuggla</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Glaucidium passerinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Brinken NV, Vstm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>564654</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6616460</v>
-      </c>
-      <c r="S16" t="n">
-        <v>50</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
